--- a/Shiny/Datos limpios/pricing_diario_trigo_2025.xlsx
+++ b/Shiny/Datos limpios/pricing_diario_trigo_2025.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K274"/>
+  <dimension ref="A1:K297"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -8785,16 +8785,16 @@
         <v>45909</v>
       </c>
       <c r="B228">
-        <v>64232.93</v>
+        <v>63632.93</v>
       </c>
       <c r="C228">
-        <v>31.7</v>
+        <v>491.02</v>
       </c>
       <c r="D228">
         <v>3067.26</v>
       </c>
       <c r="E228">
-        <v>61197.37</v>
+        <v>61056.69</v>
       </c>
       <c r="F228">
         <v>12578.03</v>
@@ -8809,7 +8809,7 @@
         <v>12485.51</v>
       </c>
       <c r="J228">
-        <v>73682.87999999999</v>
+        <v>73542.2</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
@@ -9081,16 +9081,16 @@
         <v>45917</v>
       </c>
       <c r="B236">
-        <v>137834.57</v>
+        <v>137738.57</v>
       </c>
       <c r="C236">
-        <v>310</v>
+        <v>372.08</v>
       </c>
       <c r="D236">
         <v>1580.61</v>
       </c>
       <c r="E236">
-        <v>136563.96</v>
+        <v>136530.04</v>
       </c>
       <c r="F236">
         <v>27514.66</v>
@@ -9105,7 +9105,7 @@
         <v>27630.52</v>
       </c>
       <c r="J236">
-        <v>164194.48</v>
+        <v>164160.56</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -9303,16 +9303,16 @@
         <v>45923</v>
       </c>
       <c r="B242">
-        <v>141286.59</v>
+        <v>140286.59</v>
       </c>
       <c r="C242">
-        <v>5036</v>
+        <v>5848.27</v>
       </c>
       <c r="D242">
         <v>299.14</v>
       </c>
       <c r="E242">
-        <v>146023.45</v>
+        <v>145835.72</v>
       </c>
       <c r="F242">
         <v>16622.81</v>
@@ -9327,7 +9327,7 @@
         <v>16622.81</v>
       </c>
       <c r="J242">
-        <v>162646.26</v>
+        <v>162458.53</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
@@ -9340,16 +9340,16 @@
         <v>45924</v>
       </c>
       <c r="B243">
-        <v>149305.62</v>
+        <v>148805.62</v>
       </c>
       <c r="C243">
         <v>420</v>
       </c>
       <c r="D243">
-        <v>3470</v>
+        <v>3970</v>
       </c>
       <c r="E243">
-        <v>146255.62</v>
+        <v>145255.62</v>
       </c>
       <c r="F243">
         <v>14783.58</v>
@@ -9364,7 +9364,7 @@
         <v>14843.58</v>
       </c>
       <c r="J243">
-        <v>161099.2</v>
+        <v>160099.2</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
@@ -9599,16 +9599,16 @@
         <v>45931</v>
       </c>
       <c r="B250">
-        <v>52864.42</v>
+        <v>47864.42</v>
       </c>
       <c r="C250">
-        <v>506.2</v>
+        <v>5384.71</v>
       </c>
       <c r="D250">
         <v>0</v>
       </c>
       <c r="E250">
-        <v>53370.62</v>
+        <v>53249.13</v>
       </c>
       <c r="F250">
         <v>6546.9</v>
@@ -9623,7 +9623,7 @@
         <v>6546.9</v>
       </c>
       <c r="J250">
-        <v>59917.52</v>
+        <v>59796.03</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
@@ -9676,13 +9676,13 @@
         <v>59908.66</v>
       </c>
       <c r="C252">
-        <v>4795.139999999999</v>
+        <v>4505.05</v>
       </c>
       <c r="D252">
         <v>0</v>
       </c>
       <c r="E252">
-        <v>64703.8</v>
+        <v>64413.71000000001</v>
       </c>
       <c r="F252">
         <v>5524.38</v>
@@ -9697,7 +9697,7 @@
         <v>5524.38</v>
       </c>
       <c r="J252">
-        <v>70228.18000000001</v>
+        <v>69938.09000000001</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
@@ -9821,16 +9821,16 @@
         <v>45937</v>
       </c>
       <c r="B256">
-        <v>79915.69</v>
+        <v>79715.69</v>
       </c>
       <c r="C256">
-        <v>1400</v>
+        <v>1444.73</v>
       </c>
       <c r="D256">
         <v>1063.12</v>
       </c>
       <c r="E256">
-        <v>80252.57000000001</v>
+        <v>80097.3</v>
       </c>
       <c r="F256">
         <v>7513.22</v>
@@ -9845,7 +9845,7 @@
         <v>7513.22</v>
       </c>
       <c r="J256">
-        <v>87765.79000000001</v>
+        <v>87610.52</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
@@ -10043,16 +10043,16 @@
         <v>45943</v>
       </c>
       <c r="B262">
-        <v>130553.83</v>
+        <v>128553.83</v>
       </c>
       <c r="C262">
-        <v>4259.09</v>
+        <v>5962.53</v>
       </c>
       <c r="D262">
         <v>920</v>
       </c>
       <c r="E262">
-        <v>133892.92</v>
+        <v>133596.36</v>
       </c>
       <c r="F262">
         <v>3140.11</v>
@@ -10067,7 +10067,7 @@
         <v>3240.11</v>
       </c>
       <c r="J262">
-        <v>137133.03</v>
+        <v>136836.47</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
@@ -10487,33 +10487,884 @@
         <v>45957</v>
       </c>
       <c r="B274">
-        <v>960</v>
+        <v>49420.54</v>
       </c>
       <c r="C274">
-        <v>0</v>
+        <v>890.6799999999999</v>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>2897.97</v>
       </c>
       <c r="E274">
-        <v>960</v>
+        <v>47413.25</v>
       </c>
       <c r="F274">
-        <v>0</v>
+        <v>5262.29</v>
       </c>
       <c r="G274">
         <v>0</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I274">
-        <v>0</v>
+        <v>3262.29</v>
       </c>
       <c r="J274">
-        <v>960</v>
+        <v>50675.54</v>
       </c>
       <c r="K274" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B275">
+        <v>87911.69</v>
+      </c>
+      <c r="C275">
+        <v>1599.02</v>
+      </c>
+      <c r="D275">
+        <v>760</v>
+      </c>
+      <c r="E275">
+        <v>88750.71000000001</v>
+      </c>
+      <c r="F275">
+        <v>13606.05</v>
+      </c>
+      <c r="G275">
+        <v>0</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+      <c r="I275">
+        <v>13606.05</v>
+      </c>
+      <c r="J275">
+        <v>102356.76</v>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B276">
+        <v>59342.82</v>
+      </c>
+      <c r="C276">
+        <v>528.65</v>
+      </c>
+      <c r="D276">
+        <v>1713.64</v>
+      </c>
+      <c r="E276">
+        <v>58157.83</v>
+      </c>
+      <c r="F276">
+        <v>4309.37</v>
+      </c>
+      <c r="G276">
+        <v>0</v>
+      </c>
+      <c r="H276">
+        <v>25</v>
+      </c>
+      <c r="I276">
+        <v>4284.37</v>
+      </c>
+      <c r="J276">
+        <v>62442.2</v>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B277">
+        <v>82516.25</v>
+      </c>
+      <c r="C277">
+        <v>1304.92</v>
+      </c>
+      <c r="D277">
+        <v>360</v>
+      </c>
+      <c r="E277">
+        <v>83461.17</v>
+      </c>
+      <c r="F277">
+        <v>8736.530000000001</v>
+      </c>
+      <c r="G277">
+        <v>0</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277">
+        <v>8736.530000000001</v>
+      </c>
+      <c r="J277">
+        <v>92197.7</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B278">
+        <v>78970.52</v>
+      </c>
+      <c r="C278">
+        <v>982.49</v>
+      </c>
+      <c r="D278">
+        <v>35.68</v>
+      </c>
+      <c r="E278">
+        <v>79917.33000000002</v>
+      </c>
+      <c r="F278">
+        <v>10351.99</v>
+      </c>
+      <c r="G278">
+        <v>404.46</v>
+      </c>
+      <c r="H278">
+        <v>111.56</v>
+      </c>
+      <c r="I278">
+        <v>10644.89</v>
+      </c>
+      <c r="J278">
+        <v>90562.22000000002</v>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B279">
+        <v>606.17</v>
+      </c>
+      <c r="C279">
+        <v>60</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>666.17</v>
+      </c>
+      <c r="F279">
+        <v>931.64</v>
+      </c>
+      <c r="G279">
+        <v>0</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+      <c r="I279">
+        <v>931.64</v>
+      </c>
+      <c r="J279">
+        <v>1597.81</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2">
+        <v>45963</v>
+      </c>
+      <c r="B280">
+        <v>0</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>0</v>
+      </c>
+      <c r="G280">
+        <v>0</v>
+      </c>
+      <c r="H280">
+        <v>0</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B281">
+        <v>90137.72</v>
+      </c>
+      <c r="C281">
+        <v>390</v>
+      </c>
+      <c r="D281">
+        <v>2220</v>
+      </c>
+      <c r="E281">
+        <v>88307.72</v>
+      </c>
+      <c r="F281">
+        <v>11145.39</v>
+      </c>
+      <c r="G281">
+        <v>0</v>
+      </c>
+      <c r="H281">
+        <v>0</v>
+      </c>
+      <c r="I281">
+        <v>11145.39</v>
+      </c>
+      <c r="J281">
+        <v>99453.11</v>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B282">
+        <v>67599.42999999999</v>
+      </c>
+      <c r="C282">
+        <v>5514.29</v>
+      </c>
+      <c r="D282">
+        <v>886</v>
+      </c>
+      <c r="E282">
+        <v>72227.71999999999</v>
+      </c>
+      <c r="F282">
+        <v>5552.6</v>
+      </c>
+      <c r="G282">
+        <v>0</v>
+      </c>
+      <c r="H282">
+        <v>180</v>
+      </c>
+      <c r="I282">
+        <v>5372.6</v>
+      </c>
+      <c r="J282">
+        <v>77600.31999999999</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B283">
+        <v>85270.99000000001</v>
+      </c>
+      <c r="C283">
+        <v>1550.75</v>
+      </c>
+      <c r="D283">
+        <v>1401</v>
+      </c>
+      <c r="E283">
+        <v>85420.74000000001</v>
+      </c>
+      <c r="F283">
+        <v>9871.959999999999</v>
+      </c>
+      <c r="G283">
+        <v>0</v>
+      </c>
+      <c r="H283">
+        <v>0</v>
+      </c>
+      <c r="I283">
+        <v>9871.959999999999</v>
+      </c>
+      <c r="J283">
+        <v>95292.70000000001</v>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B284">
+        <v>62794.73</v>
+      </c>
+      <c r="C284">
+        <v>1541.4</v>
+      </c>
+      <c r="D284">
+        <v>570</v>
+      </c>
+      <c r="E284">
+        <v>63766.13</v>
+      </c>
+      <c r="F284">
+        <v>7686.5</v>
+      </c>
+      <c r="G284">
+        <v>0</v>
+      </c>
+      <c r="H284">
+        <v>300</v>
+      </c>
+      <c r="I284">
+        <v>7386.5</v>
+      </c>
+      <c r="J284">
+        <v>71152.63</v>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B285">
+        <v>53014.63</v>
+      </c>
+      <c r="C285">
+        <v>1106.03</v>
+      </c>
+      <c r="D285">
+        <v>1066.87</v>
+      </c>
+      <c r="E285">
+        <v>53053.78999999999</v>
+      </c>
+      <c r="F285">
+        <v>8720.52</v>
+      </c>
+      <c r="G285">
+        <v>0</v>
+      </c>
+      <c r="H285">
+        <v>0</v>
+      </c>
+      <c r="I285">
+        <v>8720.52</v>
+      </c>
+      <c r="J285">
+        <v>61774.31</v>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2">
+        <v>45969</v>
+      </c>
+      <c r="B286">
+        <v>254.2</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>254.2</v>
+      </c>
+      <c r="F286">
+        <v>0</v>
+      </c>
+      <c r="G286">
+        <v>0</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286">
+        <v>0</v>
+      </c>
+      <c r="J286">
+        <v>254.2</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B287">
+        <v>84866.06</v>
+      </c>
+      <c r="C287">
+        <v>812</v>
+      </c>
+      <c r="D287">
+        <v>2178.62</v>
+      </c>
+      <c r="E287">
+        <v>83499.44</v>
+      </c>
+      <c r="F287">
+        <v>9012.540000000001</v>
+      </c>
+      <c r="G287">
+        <v>0</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287">
+        <v>9012.540000000001</v>
+      </c>
+      <c r="J287">
+        <v>92511.98000000001</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B288">
+        <v>84067.49000000001</v>
+      </c>
+      <c r="C288">
+        <v>881.8</v>
+      </c>
+      <c r="D288">
+        <v>210</v>
+      </c>
+      <c r="E288">
+        <v>84739.29000000001</v>
+      </c>
+      <c r="F288">
+        <v>7972.79</v>
+      </c>
+      <c r="G288">
+        <v>0</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+      <c r="I288">
+        <v>7972.79</v>
+      </c>
+      <c r="J288">
+        <v>92712.08</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B289">
+        <v>103835.3</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>1226.97</v>
+      </c>
+      <c r="E289">
+        <v>102608.33</v>
+      </c>
+      <c r="F289">
+        <v>7339.21</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289">
+        <v>7339.21</v>
+      </c>
+      <c r="J289">
+        <v>109947.54</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B290">
+        <v>132336.4</v>
+      </c>
+      <c r="C290">
+        <v>774.08</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>133110.48</v>
+      </c>
+      <c r="F290">
+        <v>12247.26</v>
+      </c>
+      <c r="G290">
+        <v>388.53</v>
+      </c>
+      <c r="H290">
+        <v>0</v>
+      </c>
+      <c r="I290">
+        <v>12635.79</v>
+      </c>
+      <c r="J290">
+        <v>145746.27</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B291">
+        <v>136705.2</v>
+      </c>
+      <c r="C291">
+        <v>710.8099999999999</v>
+      </c>
+      <c r="D291">
+        <v>4256</v>
+      </c>
+      <c r="E291">
+        <v>133160.01</v>
+      </c>
+      <c r="F291">
+        <v>26154.16</v>
+      </c>
+      <c r="G291">
+        <v>0</v>
+      </c>
+      <c r="H291">
+        <v>0</v>
+      </c>
+      <c r="I291">
+        <v>26154.16</v>
+      </c>
+      <c r="J291">
+        <v>159314.17</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B292">
+        <v>720</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+      <c r="E292">
+        <v>720</v>
+      </c>
+      <c r="F292">
+        <v>0</v>
+      </c>
+      <c r="G292">
+        <v>0</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>720</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B293">
+        <v>102306.82</v>
+      </c>
+      <c r="C293">
+        <v>665.03</v>
+      </c>
+      <c r="D293">
+        <v>440</v>
+      </c>
+      <c r="E293">
+        <v>102531.85</v>
+      </c>
+      <c r="F293">
+        <v>10884.48</v>
+      </c>
+      <c r="G293">
+        <v>0</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+      <c r="I293">
+        <v>10884.48</v>
+      </c>
+      <c r="J293">
+        <v>113416.33</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B294">
+        <v>109614.54</v>
+      </c>
+      <c r="C294">
+        <v>1716.92</v>
+      </c>
+      <c r="D294">
+        <v>590</v>
+      </c>
+      <c r="E294">
+        <v>110741.46</v>
+      </c>
+      <c r="F294">
+        <v>5898.33</v>
+      </c>
+      <c r="G294">
+        <v>0</v>
+      </c>
+      <c r="H294">
+        <v>120</v>
+      </c>
+      <c r="I294">
+        <v>5778.33</v>
+      </c>
+      <c r="J294">
+        <v>116519.79</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B295">
+        <v>123958.86</v>
+      </c>
+      <c r="C295">
+        <v>1103.01</v>
+      </c>
+      <c r="D295">
+        <v>6364</v>
+      </c>
+      <c r="E295">
+        <v>118697.87</v>
+      </c>
+      <c r="F295">
+        <v>17568.67</v>
+      </c>
+      <c r="G295">
+        <v>0</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+      <c r="I295">
+        <v>17568.67</v>
+      </c>
+      <c r="J295">
+        <v>136266.54</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B296">
+        <v>93866.78</v>
+      </c>
+      <c r="C296">
+        <v>2046.14</v>
+      </c>
+      <c r="D296">
+        <v>60</v>
+      </c>
+      <c r="E296">
+        <v>95852.92</v>
+      </c>
+      <c r="F296">
+        <v>4646.53</v>
+      </c>
+      <c r="G296">
+        <v>249.67</v>
+      </c>
+      <c r="H296">
+        <v>0</v>
+      </c>
+      <c r="I296">
+        <v>4896.2</v>
+      </c>
+      <c r="J296">
+        <v>100749.12</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B297">
+        <v>19756.07</v>
+      </c>
+      <c r="C297">
+        <v>567</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>20323.07</v>
+      </c>
+      <c r="F297">
+        <v>278.3</v>
+      </c>
+      <c r="G297">
+        <v>0</v>
+      </c>
+      <c r="H297">
+        <v>210</v>
+      </c>
+      <c r="I297">
+        <v>68.30000000000001</v>
+      </c>
+      <c r="J297">
+        <v>20391.37</v>
+      </c>
+      <c r="K297" t="inlineStr">
         <is>
           <t>TRIGO</t>
         </is>
